--- a/sample_metadata.xlsx
+++ b/sample_metadata.xlsx
@@ -8,13 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manjulat/Projects/Araichi/SkinDataAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58C13D6-F4D1-4646-A09C-C98CD5CBEA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF809B12-10C1-7140-80A3-3E1F36FE944A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10540" yWindow="660" windowWidth="19700" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9660" yWindow="660" windowWidth="20580" windowHeight="17740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Alkon_2022_Healthy_samples" sheetId="3" r:id="rId2"/>
+    <sheet name="Alkon_2022_AD_samples" sheetId="4" r:id="rId3"/>
+    <sheet name="Rojahn_2020_supplementary" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Rojahn_2020_supplementary!$A$1:$H$24</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="285">
   <si>
     <t>study</t>
   </si>
@@ -50,12 +56,6 @@
     <t>GSE147424</t>
   </si>
   <si>
-    <t>S1_LS</t>
-  </si>
-  <si>
-    <t>GSM4430459</t>
-  </si>
-  <si>
     <t>Frozen</t>
   </si>
   <si>
@@ -71,9 +71,6 @@
     <t>GSM4430461</t>
   </si>
   <si>
-    <t>S4_H</t>
-  </si>
-  <si>
     <t>GSM4430462</t>
   </si>
   <si>
@@ -86,9 +83,6 @@
     <t>GSM4430463</t>
   </si>
   <si>
-    <t>S6_H</t>
-  </si>
-  <si>
     <t>GSM4430464</t>
   </si>
   <si>
@@ -98,18 +92,12 @@
     <t>GSM4430465</t>
   </si>
   <si>
-    <t>S8_H</t>
-  </si>
-  <si>
     <t>GSM4430466</t>
   </si>
   <si>
     <t>Fresh</t>
   </si>
   <si>
-    <t>S9_H</t>
-  </si>
-  <si>
     <t>GSM4430467</t>
   </si>
   <si>
@@ -119,9 +107,6 @@
     <t>GSM4430468</t>
   </si>
   <si>
-    <t>S11_NL</t>
-  </si>
-  <si>
     <t>GSM4430469</t>
   </si>
   <si>
@@ -137,21 +122,12 @@
     <t>GSM4430471</t>
   </si>
   <si>
-    <t>S14_NL</t>
-  </si>
-  <si>
     <t>GSM4430472</t>
   </si>
   <si>
-    <t>S15_NL</t>
-  </si>
-  <si>
     <t>GSM4430473</t>
   </si>
   <si>
-    <t>S16_NL</t>
-  </si>
-  <si>
     <t>GSM4430474</t>
   </si>
   <si>
@@ -428,9 +404,6 @@
     <t>tissue collection</t>
   </si>
   <si>
-    <t>Unknown</t>
-  </si>
-  <si>
     <t>3' v2</t>
   </si>
   <si>
@@ -486,13 +459,469 @@
   </si>
   <si>
     <t>female</t>
+  </si>
+  <si>
+    <t>Biopsy</t>
+  </si>
+  <si>
+    <t>HC</t>
+  </si>
+  <si>
+    <t>Caucasian</t>
+  </si>
+  <si>
+    <t>Suction blister</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Sample type</t>
+  </si>
+  <si>
+    <t>scRNAseq</t>
+  </si>
+  <si>
+    <t>OLINK</t>
+  </si>
+  <si>
+    <t>Diagnosis</t>
+  </si>
+  <si>
+    <t>EASI</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Subject ID</t>
+  </si>
+  <si>
+    <t>technical replicate?  And not matching GSM from Rojahn_2020 paper's supplmentary tables</t>
+  </si>
+  <si>
+    <t>not matching GSM from Rojahn_2020 paper's supplmentary tables</t>
+  </si>
+  <si>
+    <t>Healthy individuals:</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Age (y.)</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Specimen</t>
+  </si>
+  <si>
+    <t>Experimental Cohort</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Skin</t>
+  </si>
+  <si>
+    <t>10XGenomics (NHS1) / IP&amp;IF</t>
+  </si>
+  <si>
+    <t>N2</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>10XGenomics (NHS2) / IP&amp;IF</t>
+  </si>
+  <si>
+    <t>N3</t>
+  </si>
+  <si>
+    <t>10XGenomics (NHS3) / FC / skin explant cultures</t>
+  </si>
+  <si>
+    <t>N4</t>
+  </si>
+  <si>
+    <t>IP&amp;IF / FC / skin explant cultures</t>
+  </si>
+  <si>
+    <t>N5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FC / skin explant cultures </t>
+  </si>
+  <si>
+    <t>N6</t>
+  </si>
+  <si>
+    <t>FC</t>
+  </si>
+  <si>
+    <t>N7</t>
+  </si>
+  <si>
+    <t>N8</t>
+  </si>
+  <si>
+    <t>N9</t>
+  </si>
+  <si>
+    <t>N10</t>
+  </si>
+  <si>
+    <t>N12</t>
+  </si>
+  <si>
+    <t>IF / FC</t>
+  </si>
+  <si>
+    <t>N13</t>
+  </si>
+  <si>
+    <t>N14</t>
+  </si>
+  <si>
+    <t>N15</t>
+  </si>
+  <si>
+    <t>IF</t>
+  </si>
+  <si>
+    <t>N16</t>
+  </si>
+  <si>
+    <t>N17</t>
+  </si>
+  <si>
+    <t>N18</t>
+  </si>
+  <si>
+    <t>N19</t>
+  </si>
+  <si>
+    <t>N20</t>
+  </si>
+  <si>
+    <t>N21</t>
+  </si>
+  <si>
+    <t>IP&amp;IF</t>
+  </si>
+  <si>
+    <t>N22</t>
+  </si>
+  <si>
+    <t>N23</t>
+  </si>
+  <si>
+    <t>N24</t>
+  </si>
+  <si>
+    <t>N25</t>
+  </si>
+  <si>
+    <t>Blood</t>
+  </si>
+  <si>
+    <t>FC / ILCs expansion / RT-PCR</t>
+  </si>
+  <si>
+    <t>N26</t>
+  </si>
+  <si>
+    <t>N27</t>
+  </si>
+  <si>
+    <t>N28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FC </t>
+  </si>
+  <si>
+    <t>N29</t>
+  </si>
+  <si>
+    <t>N30</t>
+  </si>
+  <si>
+    <t>N31</t>
+  </si>
+  <si>
+    <t>FC / ILCs expansion</t>
+  </si>
+  <si>
+    <t>N32</t>
+  </si>
+  <si>
+    <t>N33</t>
+  </si>
+  <si>
+    <t>N34</t>
+  </si>
+  <si>
+    <t>N35</t>
+  </si>
+  <si>
+    <t>N36</t>
+  </si>
+  <si>
+    <t>N37</t>
+  </si>
+  <si>
+    <t>N38</t>
+  </si>
+  <si>
+    <t>N39</t>
+  </si>
+  <si>
+    <t>N40</t>
+  </si>
+  <si>
+    <t>N41</t>
+  </si>
+  <si>
+    <t>N42</t>
+  </si>
+  <si>
+    <t>N43</t>
+  </si>
+  <si>
+    <t>N44</t>
+  </si>
+  <si>
+    <t>N45</t>
+  </si>
+  <si>
+    <t>N46</t>
+  </si>
+  <si>
+    <t>N47</t>
+  </si>
+  <si>
+    <t>N48</t>
+  </si>
+  <si>
+    <t>N49</t>
+  </si>
+  <si>
+    <t>ILCs expansion / RT-PCR</t>
+  </si>
+  <si>
+    <t>N50</t>
+  </si>
+  <si>
+    <t>N51</t>
+  </si>
+  <si>
+    <t>N52</t>
+  </si>
+  <si>
+    <t>Atopic dermatitis patients:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGA </t>
+  </si>
+  <si>
+    <t>(0-4)</t>
+  </si>
+  <si>
+    <r>
+      <t>WBC, 10</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/L</t>
+    </r>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>10XGenomics (AD2)</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>10XGenomics (AD3)</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>10XGenomics (AD4) / FC</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>Skin //</t>
+  </si>
+  <si>
+    <t>10XGenomics (AD5) // ILCs expansion</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>IP&amp;IF // ILCs expansion</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ILCs expansion</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skin </t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ </t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP&amp;IF </t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>A16</t>
+  </si>
+  <si>
+    <t>A17</t>
+  </si>
+  <si>
+    <t>A18</t>
+  </si>
+  <si>
+    <t>A19</t>
+  </si>
+  <si>
+    <t>A20</t>
+  </si>
+  <si>
+    <t>A21</t>
+  </si>
+  <si>
+    <t>A22</t>
+  </si>
+  <si>
+    <t>A23</t>
+  </si>
+  <si>
+    <t>S1_LS </t>
+  </si>
+  <si>
+    <t>S4_H </t>
+  </si>
+  <si>
+    <t>S6_H </t>
+  </si>
+  <si>
+    <t>S8_H </t>
+  </si>
+  <si>
+    <t>S9_H </t>
+  </si>
+  <si>
+    <t>S11_NL </t>
+  </si>
+  <si>
+    <t>S14_NL </t>
+  </si>
+  <si>
+    <t>S15_NL </t>
+  </si>
+  <si>
+    <t>S16_NL </t>
+  </si>
+  <si>
+    <t>GSM4430459    </t>
+  </si>
+  <si>
+    <t>Frozen  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -501,9 +930,77 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -517,7 +1014,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -525,16 +1022,187 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{BF9F7201-FB98-7644-A3FA-D8F6BCFC6E6C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -846,25 +1514,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>2</v>
@@ -873,36 +1541,36 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J2">
         <v>34.200000000000003</v>
@@ -910,136 +1578,136 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J3">
         <v>15.9</v>
       </c>
       <c r="K3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C4">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J4">
         <v>10.1</v>
       </c>
       <c r="K4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C5">
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J5">
         <v>2.4</v>
       </c>
       <c r="K5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C6">
         <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F6" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G6" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J6">
         <v>27.4</v>
@@ -1047,241 +1715,241 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C7">
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H7" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J7">
         <v>3.2</v>
       </c>
       <c r="K7" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C8">
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H8" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J8">
         <v>2.6</v>
       </c>
       <c r="K8" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C9">
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H9" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J9">
         <v>1.1000000000000001</v>
       </c>
       <c r="K9" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C10">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J10">
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C11">
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J11">
         <v>5.4</v>
       </c>
       <c r="K11" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C12">
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H12" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J12">
         <v>11.2</v>
       </c>
       <c r="K12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G13" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I13" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J13">
         <v>44.6</v>
@@ -1289,31 +1957,31 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" t="s">
         <v>122</v>
-      </c>
-      <c r="G14" t="s">
-        <v>126</v>
-      </c>
-      <c r="H14" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" t="s">
-        <v>133</v>
       </c>
       <c r="J14">
         <v>44.6</v>
@@ -1321,135 +1989,159 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>48</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G15" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I15" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>52</v>
+      </c>
+      <c r="C16">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>139</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="K16" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="C17">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I17" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="K17" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
         <v>57</v>
       </c>
-      <c r="B18" t="s">
-        <v>67</v>
+      <c r="C18">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H18" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I18" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="K18" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G19" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I19" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J19">
         <v>44.7</v>
@@ -1457,31 +2149,31 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" t="s">
         <v>122</v>
-      </c>
-      <c r="G20" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s">
-        <v>133</v>
       </c>
       <c r="J20">
         <v>44.7</v>
@@ -1489,938 +2181,3541 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" t="s">
         <v>122</v>
-      </c>
-      <c r="G21" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" t="s">
-        <v>61</v>
-      </c>
-      <c r="I21" t="s">
-        <v>133</v>
       </c>
       <c r="J21">
         <v>5.5</v>
       </c>
+      <c r="K21" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" t="s">
         <v>122</v>
-      </c>
-      <c r="G22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" t="s">
-        <v>133</v>
       </c>
       <c r="J22">
         <v>5.5</v>
       </c>
+      <c r="K22" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>45</v>
+      </c>
+      <c r="C23">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>139</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" t="s">
         <v>122</v>
-      </c>
-      <c r="G23" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" t="s">
-        <v>133</v>
       </c>
       <c r="J23">
         <v>24.1</v>
       </c>
       <c r="K23" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" t="s">
         <v>122</v>
-      </c>
-      <c r="G24" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" t="s">
-        <v>133</v>
       </c>
       <c r="J24">
         <v>24.1</v>
       </c>
       <c r="K24" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>67</v>
+      </c>
+      <c r="C25" s="10">
+        <v>22</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" t="s">
         <v>122</v>
-      </c>
-      <c r="G25" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" t="s">
-        <v>76</v>
-      </c>
-      <c r="I25" t="s">
-        <v>133</v>
       </c>
       <c r="J25">
         <v>28.1</v>
       </c>
+      <c r="K25" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
         <v>69</v>
       </c>
-      <c r="B26" t="s">
-        <v>79</v>
+      <c r="C26" s="10">
+        <v>24</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" t="s">
         <v>122</v>
-      </c>
-      <c r="G26" t="s">
-        <v>126</v>
-      </c>
-      <c r="H26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" t="s">
-        <v>133</v>
       </c>
       <c r="J26">
         <v>42.8</v>
       </c>
+      <c r="K26" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>71</v>
+      </c>
+      <c r="C27" s="10">
+        <v>42</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" t="s">
+        <v>66</v>
+      </c>
+      <c r="I27" t="s">
         <v>122</v>
-      </c>
-      <c r="G27" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" t="s">
-        <v>133</v>
       </c>
       <c r="J27">
         <v>46.5</v>
       </c>
+      <c r="K27" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C28">
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H28" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I28" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K28" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C29">
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I29" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E30" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H30" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I30" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C31">
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H31" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I31" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C32">
         <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I32" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J32" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>84</v>
+      </c>
+      <c r="C33" s="10">
+        <v>27</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I33" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>75</v>
+      </c>
+      <c r="K33" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="C34" s="10">
+        <v>42</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="E34" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H34" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I34" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
+        <v>75</v>
+      </c>
+      <c r="K34" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>33</v>
+      </c>
+      <c r="C35">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
+        <v>139</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="I35" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>24</v>
+      </c>
+      <c r="D36" t="s">
+        <v>138</v>
       </c>
       <c r="E36" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H36" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="I36" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>37</v>
+      </c>
+      <c r="C37">
+        <v>37</v>
+      </c>
+      <c r="D37" t="s">
+        <v>138</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="I37" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>4</v>
       </c>
-      <c r="B38" t="s">
-        <v>5</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>122</v>
+      <c r="B38" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="G38" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H38" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I38" t="s">
-        <v>131</v>
-      </c>
-      <c r="K38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K38" s="23" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>4</v>
       </c>
-      <c r="B39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
+      <c r="B39" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="G39" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H39" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>131</v>
-      </c>
-      <c r="K39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K39" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>4</v>
       </c>
-      <c r="B40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" t="s">
-        <v>29</v>
-      </c>
-      <c r="F40" t="s">
-        <v>123</v>
+      <c r="B40" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>113</v>
       </c>
       <c r="G40" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H40" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>131</v>
-      </c>
-      <c r="K40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K40" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>4</v>
       </c>
-      <c r="B41" t="s">
-        <v>30</v>
-      </c>
-      <c r="E41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" t="s">
-        <v>14</v>
+      <c r="B41" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H41" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I41" t="s">
-        <v>131</v>
-      </c>
-      <c r="K41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K41" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>4</v>
       </c>
-      <c r="B42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" t="s">
-        <v>14</v>
+      <c r="B42" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="G42" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H42" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I42" t="s">
-        <v>131</v>
-      </c>
-      <c r="K42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K42" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>4</v>
       </c>
-      <c r="B43" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" t="s">
-        <v>35</v>
-      </c>
-      <c r="F43" t="s">
-        <v>123</v>
+      <c r="B43" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H43" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I43" t="s">
-        <v>131</v>
-      </c>
-      <c r="K43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K43" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>4</v>
       </c>
-      <c r="B44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" t="s">
-        <v>37</v>
-      </c>
-      <c r="F44" t="s">
-        <v>123</v>
+      <c r="B44" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="G44" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H44" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I44" t="s">
-        <v>131</v>
-      </c>
-      <c r="K44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K44" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>4</v>
       </c>
-      <c r="B45" t="s">
-        <v>38</v>
-      </c>
-      <c r="E45" t="s">
-        <v>39</v>
-      </c>
-      <c r="F45" t="s">
-        <v>123</v>
+      <c r="B45" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H45" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I45" t="s">
-        <v>131</v>
-      </c>
-      <c r="K45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K45" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>4</v>
       </c>
-      <c r="B46" t="s">
-        <v>40</v>
-      </c>
-      <c r="E46" t="s">
-        <v>41</v>
-      </c>
-      <c r="F46" t="s">
-        <v>14</v>
+      <c r="B46" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H46" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I46" t="s">
-        <v>131</v>
-      </c>
-      <c r="K46" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K46" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>4</v>
       </c>
-      <c r="B47" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>122</v>
+      <c r="B47" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H47" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I47" t="s">
-        <v>131</v>
-      </c>
-      <c r="K47" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K47" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>4</v>
       </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
-        <v>123</v>
+      <c r="B48" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>112</v>
       </c>
       <c r="G48" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H48" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I48" t="s">
-        <v>131</v>
-      </c>
-      <c r="K48" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K48" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>4</v>
       </c>
-      <c r="B49" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" t="s">
-        <v>14</v>
+      <c r="B49" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H49" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I49" t="s">
-        <v>131</v>
-      </c>
-      <c r="K49" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K49" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>4</v>
       </c>
-      <c r="B50" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" t="s">
-        <v>122</v>
+      <c r="B50" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H50" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I50" t="s">
-        <v>131</v>
-      </c>
-      <c r="K50" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K50" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>4</v>
       </c>
-      <c r="B51" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" t="s">
-        <v>14</v>
+      <c r="B51" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>112</v>
       </c>
       <c r="G51" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H51" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I51" t="s">
-        <v>131</v>
-      </c>
-      <c r="K51" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K51" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>4</v>
       </c>
-      <c r="B52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" t="s">
-        <v>20</v>
-      </c>
-      <c r="F52" t="s">
-        <v>122</v>
+      <c r="B52" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>112</v>
       </c>
       <c r="G52" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H52" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I52" t="s">
-        <v>131</v>
-      </c>
-      <c r="K52" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K52" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>4</v>
       </c>
-      <c r="B53" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" t="s">
-        <v>22</v>
-      </c>
-      <c r="F53" t="s">
-        <v>14</v>
+      <c r="B53" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>112</v>
       </c>
       <c r="G53" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H53" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I53" t="s">
-        <v>131</v>
-      </c>
-      <c r="K53" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="K53" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>4</v>
       </c>
-      <c r="B54" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" t="s">
-        <v>14</v>
+      <c r="B54" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H54" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I54" t="s">
-        <v>131</v>
-      </c>
-      <c r="K54" t="s">
-        <v>7</v>
+        <v>121</v>
+      </c>
+      <c r="K54" s="23" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L54">
     <sortCondition ref="B2:B54"/>
   </sortState>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B678B58-7994-8A40-A2D6-D3E124507B3C}">
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+    </row>
+    <row r="5" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="12">
+        <v>25</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="12">
+        <v>24</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="76" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="12">
+        <v>37</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="12">
+        <v>31</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="12">
+        <v>50</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="12">
+        <v>55</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="12">
+        <v>57</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="12">
+        <v>39</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="12">
+        <v>35</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="12">
+        <v>73</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="12">
+        <v>42</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="12">
+        <v>36</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" s="12">
+        <v>52</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="12">
+        <v>47</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="12">
+        <v>25</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="12">
+        <v>39</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="12">
+        <v>44</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="12">
+        <v>51</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="12">
+        <v>20</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="12">
+        <v>34</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="12">
+        <v>31</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" s="12">
+        <v>42</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B27" s="12">
+        <v>58</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B28" s="12">
+        <v>25</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="12">
+        <v>26</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" s="12">
+        <v>43</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B31" s="12">
+        <v>42</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" s="12">
+        <v>47</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B33" s="12">
+        <v>49</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="12">
+        <v>28</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" s="12">
+        <v>24</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B36" s="12">
+        <v>36</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B37" s="12">
+        <v>27</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B38" s="12">
+        <v>40</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" s="12">
+        <v>28</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B40" s="12">
+        <v>39</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" s="12">
+        <v>54</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B42" s="12">
+        <v>30</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B43" s="12">
+        <v>41</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" s="12">
+        <v>26</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="12">
+        <v>25</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B46" s="12">
+        <v>24</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="12">
+        <v>31</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B48" s="12">
+        <v>26</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B49" s="12">
+        <v>33</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B50" s="12">
+        <v>50</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B51" s="12">
+        <v>50</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B52" s="12">
+        <v>39</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B53" s="12">
+        <v>31</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B54" s="12">
+        <v>32</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B55" s="12">
+        <v>33</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC0462BB-2EF8-744E-A457-D2CA86DE6E2E}">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="10" max="10" width="26.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+    </row>
+    <row r="5" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="12">
+        <v>30</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="12">
+        <v>28.4</v>
+      </c>
+      <c r="E5" s="12">
+        <v>4</v>
+      </c>
+      <c r="F5" s="12">
+        <v>6.19</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="12">
+        <v>22</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="12">
+        <v>28.1</v>
+      </c>
+      <c r="E6" s="12">
+        <v>3</v>
+      </c>
+      <c r="F6" s="12">
+        <v>6.28</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="12">
+        <v>26</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="12">
+        <v>58.4</v>
+      </c>
+      <c r="E7" s="12">
+        <v>4</v>
+      </c>
+      <c r="F7" s="12">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="12">
+        <v>42</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="12">
+        <v>46</v>
+      </c>
+      <c r="E8" s="12">
+        <v>4</v>
+      </c>
+      <c r="F8" s="12">
+        <v>12.79</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="20">
+        <v>24</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="20">
+        <v>28.1</v>
+      </c>
+      <c r="E9" s="20">
+        <v>3</v>
+      </c>
+      <c r="F9" s="20">
+        <v>11.53</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="J10" s="21"/>
+    </row>
+    <row r="11" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="20">
+        <v>56</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="20">
+        <v>24.6</v>
+      </c>
+      <c r="E11" s="20">
+        <v>3</v>
+      </c>
+      <c r="F11" s="20">
+        <v>9.16</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="J12" s="21"/>
+    </row>
+    <row r="13" spans="1:10" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="12">
+        <v>27</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="E13" s="12">
+        <v>2</v>
+      </c>
+      <c r="F13" s="12">
+        <v>6.72</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="12">
+        <v>59</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="12">
+        <v>50</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E15" s="12">
+        <v>3</v>
+      </c>
+      <c r="F15" s="12">
+        <v>6.43</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="12">
+        <v>28</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E16" s="12">
+        <v>4</v>
+      </c>
+      <c r="F16" s="12">
+        <v>11.51</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="20">
+        <v>52</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="20">
+        <v>27.4</v>
+      </c>
+      <c r="E17" s="20">
+        <v>4</v>
+      </c>
+      <c r="F17" s="20">
+        <v>5.21</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+    </row>
+    <row r="19" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B19" s="12">
+        <v>23</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="12">
+        <v>6.8</v>
+      </c>
+      <c r="E19" s="12">
+        <v>2</v>
+      </c>
+      <c r="F19" s="12">
+        <v>10.11</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B29" s="12">
+        <v>46</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="12">
+        <v>26.1</v>
+      </c>
+      <c r="E29" s="12">
+        <v>4</v>
+      </c>
+      <c r="F29" s="12">
+        <v>8.65</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B30" s="12">
+        <v>51</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="12">
+        <v>43.6</v>
+      </c>
+      <c r="E30" s="12">
+        <v>4</v>
+      </c>
+      <c r="F30" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52E614A-514A-114E-8972-B06F30BD00D9}">
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>32</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="4">
+        <v>33.6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="4">
+        <v>24.1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="4">
+        <v>24.4</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="4">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="4">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="4">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="4">
+        <v>44.6</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="4">
+        <v>44.7</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
+        <v>33</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>31</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="4">
+        <v>24.1</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="4">
+        <v>28.1</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>24</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="4">
+        <v>42.8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>42</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
+        <v>40</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
+        <v>42</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4">
+        <v>47</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5">
+        <v>49</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4">
+        <v>39</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4">
+        <v>42</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+</worksheet>
 </file>
--- a/sample_metadata.xlsx
+++ b/sample_metadata.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aramasamy\Documents\SingleCellSkinAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manjulat/Projects/Araichi/SkinDataAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A45B97-F992-4B3D-B4A1-FBC5F8F68931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80059A8B-C224-BE47-920E-381FEFDC56F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="608" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13900" tabRatio="608" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="study level" sheetId="5" r:id="rId1"/>
     <sheet name="sample level" sheetId="1" r:id="rId2"/>
-    <sheet name="Alkon_2022_Healthy" sheetId="3" r:id="rId3"/>
-    <sheet name="Alkon_2022_AD" sheetId="4" r:id="rId4"/>
-    <sheet name="Rojahn_2020" sheetId="2" r:id="rId5"/>
+    <sheet name="He_2020" sheetId="6" r:id="rId3"/>
+    <sheet name="Rojahn_2020" sheetId="2" r:id="rId4"/>
+    <sheet name="Rindler_2021" sheetId="7" r:id="rId5"/>
+    <sheet name="Bangert_2021" sheetId="8" r:id="rId6"/>
+    <sheet name="Alkon_2022_Healthy" sheetId="3" r:id="rId7"/>
+    <sheet name="Alkon_2022_AD" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rojahn_2020!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Rojahn_2020!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="325">
   <si>
     <t>geo_accession</t>
   </si>
@@ -1195,7 +1198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
@@ -1218,31 +1221,29 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1269,9 +1270,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1292,6 +1290,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>671326</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>42672</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>171709</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>21019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57779EBF-9315-4AED-0F3F-BEF03092C60D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5645662" y="408432"/>
+          <a:ext cx="5401311" cy="4367467"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1329,55 +1376,6 @@
         <a:xfrm>
           <a:off x="7917180" y="250448"/>
           <a:ext cx="5216151" cy="3811011"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>671326</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>42672</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>171709</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>21019</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57779EBF-9315-4AED-0F3F-BEF03092C60D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5645662" y="408432"/>
-          <a:ext cx="5401311" cy="4367467"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1669,212 +1667,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07308A57-861E-4948-8A57-F4E50F2E460A}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" style="27" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" style="27" customWidth="1"/>
-    <col min="9" max="9" width="23" style="24" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="255.77734375" style="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="24"/>
+    <col min="1" max="1" width="13.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="25" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="23" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.1640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="255.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="21" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="22">
         <v>32035984</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="25">
         <v>8</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="25">
         <v>4</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="25">
         <v>5</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="27">
         <v>39600</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="27">
         <v>18433</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>247</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="22" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="22">
         <v>32344053</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="26">
         <v>7</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="26">
         <v>8</v>
       </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29">
+      <c r="F3" s="26"/>
+      <c r="G3" s="27">
         <v>57607</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="27">
         <v>24984</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="22" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="22">
         <v>33717163</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="25">
         <v>4</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="27">
         <v>2637</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="27">
         <v>18403</v>
       </c>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="22" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="22">
         <v>33483337</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="25">
         <v>10</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="27">
         <v>19379</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="27">
         <v>22176</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="I5" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="22" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="22">
         <v>34363841</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="25">
         <v>3</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="25">
         <v>4</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="27">
         <v>25034</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="27">
         <v>19195</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="22" t="s">
         <v>248</v>
       </c>
     </row>
@@ -1889,21 +1887,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M54"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.77734375" customWidth="1"/>
-    <col min="7" max="7" width="23.109375" customWidth="1"/>
+    <col min="5" max="6" width="6.83203125" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="31"/>
+    <col min="11" max="11" width="11.5" style="19"/>
     <col min="12" max="12" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>239</v>
       </c>
@@ -1934,15 +1932,15 @@
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="28" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B2" t="s">
@@ -1954,6 +1952,12 @@
       <c r="D2" s="10" t="s">
         <v>308</v>
       </c>
+      <c r="E2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2" t="s">
+        <v>218</v>
+      </c>
       <c r="G2" s="10" t="s">
         <v>86</v>
       </c>
@@ -1966,12 +1970,18 @@
       <c r="J2" t="s">
         <v>94</v>
       </c>
+      <c r="K2" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L2" s="10" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="M2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B3" t="s">
@@ -1983,6 +1993,12 @@
       <c r="D3" s="10" t="s">
         <v>309</v>
       </c>
+      <c r="E3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F3" t="s">
+        <v>218</v>
+      </c>
       <c r="G3" s="10" t="s">
         <v>8</v>
       </c>
@@ -1995,12 +2011,18 @@
       <c r="J3" t="s">
         <v>94</v>
       </c>
+      <c r="K3" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L3" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="M3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B4" t="s">
@@ -2012,6 +2034,12 @@
       <c r="D4" s="10" t="s">
         <v>310</v>
       </c>
+      <c r="E4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" t="s">
+        <v>218</v>
+      </c>
       <c r="G4" s="11" t="s">
         <v>86</v>
       </c>
@@ -2024,12 +2052,18 @@
       <c r="J4" t="s">
         <v>94</v>
       </c>
+      <c r="K4" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L4" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="M4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B5" t="s">
@@ -2041,6 +2075,12 @@
       <c r="D5" s="10" t="s">
         <v>311</v>
       </c>
+      <c r="E5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" t="s">
+        <v>218</v>
+      </c>
       <c r="G5" s="10" t="s">
         <v>8</v>
       </c>
@@ -2053,12 +2093,18 @@
       <c r="J5" t="s">
         <v>94</v>
       </c>
+      <c r="K5" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L5" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="M5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B6" t="s">
@@ -2070,6 +2116,12 @@
       <c r="D6" s="10" t="s">
         <v>312</v>
       </c>
+      <c r="E6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" t="s">
+        <v>218</v>
+      </c>
       <c r="G6" s="10" t="s">
         <v>8</v>
       </c>
@@ -2082,12 +2134,18 @@
       <c r="J6" t="s">
         <v>94</v>
       </c>
+      <c r="K6" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L6" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="M6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B7" t="s">
@@ -2099,6 +2157,12 @@
       <c r="D7" s="10" t="s">
         <v>313</v>
       </c>
+      <c r="E7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F7" t="s">
+        <v>218</v>
+      </c>
       <c r="G7" s="11" t="s">
         <v>86</v>
       </c>
@@ -2111,12 +2175,18 @@
       <c r="J7" t="s">
         <v>94</v>
       </c>
+      <c r="K7" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L7" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="M7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B8" t="s">
@@ -2128,6 +2198,12 @@
       <c r="D8" s="10" t="s">
         <v>314</v>
       </c>
+      <c r="E8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" t="s">
+        <v>218</v>
+      </c>
       <c r="G8" s="11" t="s">
         <v>86</v>
       </c>
@@ -2140,12 +2216,18 @@
       <c r="J8" t="s">
         <v>94</v>
       </c>
+      <c r="K8" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L8" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="M8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B9" t="s">
@@ -2157,6 +2239,12 @@
       <c r="D9" s="10" t="s">
         <v>315</v>
       </c>
+      <c r="E9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" t="s">
+        <v>218</v>
+      </c>
       <c r="G9" s="11" t="s">
         <v>86</v>
       </c>
@@ -2169,12 +2257,18 @@
       <c r="J9" t="s">
         <v>94</v>
       </c>
+      <c r="K9" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L9" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
+      <c r="M9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B10" t="s">
@@ -2186,6 +2280,12 @@
       <c r="D10" s="10" t="s">
         <v>316</v>
       </c>
+      <c r="E10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" t="s">
+        <v>218</v>
+      </c>
       <c r="G10" s="10" t="s">
         <v>8</v>
       </c>
@@ -2198,12 +2298,18 @@
       <c r="J10" t="s">
         <v>94</v>
       </c>
+      <c r="K10" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L10" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="M10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B11" t="s">
@@ -2215,6 +2321,12 @@
       <c r="D11" s="10" t="s">
         <v>317</v>
       </c>
+      <c r="E11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" t="s">
+        <v>218</v>
+      </c>
       <c r="G11" s="10" t="s">
         <v>86</v>
       </c>
@@ -2227,12 +2339,18 @@
       <c r="J11" t="s">
         <v>94</v>
       </c>
+      <c r="K11" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L11" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="M11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B12" t="s">
@@ -2244,6 +2362,12 @@
       <c r="D12" s="10" t="s">
         <v>318</v>
       </c>
+      <c r="E12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" t="s">
+        <v>218</v>
+      </c>
       <c r="G12" s="10" t="s">
         <v>87</v>
       </c>
@@ -2256,12 +2380,18 @@
       <c r="J12" t="s">
         <v>94</v>
       </c>
+      <c r="K12" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L12" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="M12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B13" t="s">
@@ -2273,6 +2403,12 @@
       <c r="D13" s="10" t="s">
         <v>319</v>
       </c>
+      <c r="E13" t="s">
+        <v>218</v>
+      </c>
+      <c r="F13" t="s">
+        <v>218</v>
+      </c>
       <c r="G13" s="10" t="s">
         <v>8</v>
       </c>
@@ -2285,12 +2421,18 @@
       <c r="J13" t="s">
         <v>94</v>
       </c>
+      <c r="K13" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L13" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="M13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B14" t="s">
@@ -2302,6 +2444,12 @@
       <c r="D14" s="10" t="s">
         <v>320</v>
       </c>
+      <c r="E14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" t="s">
+        <v>218</v>
+      </c>
       <c r="G14" s="10" t="s">
         <v>86</v>
       </c>
@@ -2314,12 +2462,18 @@
       <c r="J14" t="s">
         <v>94</v>
       </c>
+      <c r="K14" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L14" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
+      <c r="M14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B15" t="s">
@@ -2331,6 +2485,12 @@
       <c r="D15" s="10" t="s">
         <v>321</v>
       </c>
+      <c r="E15" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" t="s">
+        <v>218</v>
+      </c>
       <c r="G15" s="10" t="s">
         <v>8</v>
       </c>
@@ -2343,12 +2503,18 @@
       <c r="J15" t="s">
         <v>94</v>
       </c>
+      <c r="K15" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L15" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="M15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B16" t="s">
@@ -2360,6 +2526,12 @@
       <c r="D16" s="10" t="s">
         <v>322</v>
       </c>
+      <c r="E16" t="s">
+        <v>218</v>
+      </c>
+      <c r="F16" t="s">
+        <v>218</v>
+      </c>
       <c r="G16" s="10" t="s">
         <v>86</v>
       </c>
@@ -2372,12 +2544,18 @@
       <c r="J16" t="s">
         <v>94</v>
       </c>
+      <c r="K16" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L16" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="M16" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B17" t="s">
@@ -2389,6 +2567,12 @@
       <c r="D17" s="10" t="s">
         <v>323</v>
       </c>
+      <c r="E17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F17" t="s">
+        <v>218</v>
+      </c>
       <c r="G17" s="10" t="s">
         <v>8</v>
       </c>
@@ -2401,12 +2585,18 @@
       <c r="J17" t="s">
         <v>94</v>
       </c>
+      <c r="K17" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L17" s="10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="M17" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B18" t="s">
@@ -2418,6 +2608,12 @@
       <c r="D18" s="10" t="s">
         <v>324</v>
       </c>
+      <c r="E18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F18" t="s">
+        <v>218</v>
+      </c>
       <c r="G18" s="10" t="s">
         <v>8</v>
       </c>
@@ -2430,12 +2626,18 @@
       <c r="J18" t="s">
         <v>94</v>
       </c>
+      <c r="K18" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L18" s="10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="M18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B19" t="s">
@@ -2465,12 +2667,15 @@
       <c r="J19" t="s">
         <v>94</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="19">
         <v>34.200000000000003</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="M19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B20" t="s">
@@ -2500,12 +2705,15 @@
       <c r="J20" t="s">
         <v>94</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="19">
         <v>44.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="M20" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B21" t="s">
@@ -2535,12 +2743,15 @@
       <c r="J21" t="s">
         <v>94</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="19">
         <v>44.7</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="M21" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B22" t="s">
@@ -2570,12 +2781,15 @@
       <c r="J22" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="19">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="M22" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B23" t="s">
@@ -2605,12 +2819,15 @@
       <c r="J23" t="s">
         <v>95</v>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="19">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+      <c r="M23" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B24" t="s">
@@ -2640,12 +2857,15 @@
       <c r="J24" t="s">
         <v>95</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="19">
         <v>28.1</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
+      <c r="M24" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B25" t="s">
@@ -2675,12 +2895,15 @@
       <c r="J25" t="s">
         <v>95</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="19">
         <v>42.8</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="M25" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B26" t="s">
@@ -2710,12 +2933,15 @@
       <c r="J26" t="s">
         <v>95</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="19">
         <v>46.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="M26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B27" t="s">
@@ -2745,12 +2971,15 @@
       <c r="J27" t="s">
         <v>94</v>
       </c>
-      <c r="K27" s="31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+      <c r="K27" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M27" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B28" t="s">
@@ -2780,12 +3009,15 @@
       <c r="J28" t="s">
         <v>94</v>
       </c>
-      <c r="K28" s="31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="K28" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M28" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B29" t="s">
@@ -2815,12 +3047,15 @@
       <c r="J29" t="s">
         <v>94</v>
       </c>
-      <c r="K29" s="31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
+      <c r="K29" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B30" t="s">
@@ -2850,12 +3085,15 @@
       <c r="J30" t="s">
         <v>94</v>
       </c>
-      <c r="K30" s="31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
+      <c r="K30" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M30" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B31" t="s">
@@ -2885,12 +3123,15 @@
       <c r="J31" t="s">
         <v>95</v>
       </c>
-      <c r="K31" s="31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
+      <c r="K31" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M31" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B32" t="s">
@@ -2920,12 +3161,15 @@
       <c r="J32" t="s">
         <v>95</v>
       </c>
-      <c r="K32" s="31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
+      <c r="K32" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="22" t="s">
         <v>258</v>
       </c>
       <c r="B33" t="s">
@@ -2955,12 +3199,15 @@
       <c r="J33" t="s">
         <v>95</v>
       </c>
-      <c r="K33" s="31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
+      <c r="K33" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M33" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="22" t="s">
         <v>257</v>
       </c>
       <c r="B34" t="s">
@@ -2990,12 +3237,18 @@
       <c r="J34" t="s">
         <v>95</v>
       </c>
+      <c r="K34" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L34" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
+      <c r="M34" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="22" t="s">
         <v>257</v>
       </c>
       <c r="B35" t="s">
@@ -3025,12 +3278,18 @@
       <c r="J35" t="s">
         <v>95</v>
       </c>
+      <c r="K35" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L35" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
+      <c r="M35" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="22" t="s">
         <v>257</v>
       </c>
       <c r="B36" t="s">
@@ -3060,12 +3319,18 @@
       <c r="J36" t="s">
         <v>95</v>
       </c>
+      <c r="K36" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L36" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
+      <c r="M36" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="22" t="s">
         <v>257</v>
       </c>
       <c r="B37" t="s">
@@ -3095,12 +3360,18 @@
       <c r="J37" t="s">
         <v>95</v>
       </c>
+      <c r="K37" s="19" t="s">
+        <v>218</v>
+      </c>
       <c r="L37" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
+      <c r="M37" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B38" t="s">
@@ -3130,15 +3401,15 @@
       <c r="J38" t="s">
         <v>95</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="19">
         <v>15.9</v>
       </c>
       <c r="L38" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+    <row r="39" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B39" t="s">
@@ -3168,15 +3439,15 @@
       <c r="J39" t="s">
         <v>95</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="19">
         <v>10.1</v>
       </c>
       <c r="L39" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+    <row r="40" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B40" t="s">
@@ -3206,15 +3477,15 @@
       <c r="J40" t="s">
         <v>95</v>
       </c>
-      <c r="K40" s="31">
+      <c r="K40" s="19">
         <v>2.4</v>
       </c>
       <c r="L40" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
+    <row r="41" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B41" t="s">
@@ -3244,12 +3515,12 @@
       <c r="J41" t="s">
         <v>95</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="19">
         <v>27.4</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
+    <row r="42" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B42" t="s">
@@ -3279,15 +3550,15 @@
       <c r="J42" t="s">
         <v>95</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="19">
         <v>3.2</v>
       </c>
       <c r="L42" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
+    <row r="43" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B43" t="s">
@@ -3317,15 +3588,15 @@
       <c r="J43" t="s">
         <v>95</v>
       </c>
-      <c r="K43" s="31">
+      <c r="K43" s="19">
         <v>2.6</v>
       </c>
       <c r="L43" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
+    <row r="44" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B44" t="s">
@@ -3355,15 +3626,15 @@
       <c r="J44" t="s">
         <v>95</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="19">
         <v>1.1000000000000001</v>
       </c>
       <c r="L44" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="24" t="s">
+    <row r="45" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B45" t="s">
@@ -3393,15 +3664,15 @@
       <c r="J45" t="s">
         <v>95</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="19">
         <v>9</v>
       </c>
       <c r="L45" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
+    <row r="46" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B46" t="s">
@@ -3431,15 +3702,15 @@
       <c r="J46" t="s">
         <v>95</v>
       </c>
-      <c r="K46" s="31">
+      <c r="K46" s="19">
         <v>5.4</v>
       </c>
       <c r="L46" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
+    <row r="47" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B47" t="s">
@@ -3469,15 +3740,15 @@
       <c r="J47" t="s">
         <v>95</v>
       </c>
-      <c r="K47" s="31">
+      <c r="K47" s="19">
         <v>11.2</v>
       </c>
       <c r="L47" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+    <row r="48" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="22" t="s">
         <v>256</v>
       </c>
       <c r="B48" t="s">
@@ -3489,10 +3760,10 @@
       <c r="D48" t="s">
         <v>269</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E48" s="18">
         <v>22</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="18" t="s">
         <v>109</v>
       </c>
       <c r="G48" t="s">
@@ -3507,15 +3778,15 @@
       <c r="J48" t="s">
         <v>95</v>
       </c>
-      <c r="K48" s="20">
+      <c r="K48" s="18">
         <v>28.1</v>
       </c>
       <c r="M48" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="24" t="s">
+    <row r="49" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="22" t="s">
         <v>256</v>
       </c>
       <c r="B49" t="s">
@@ -3527,10 +3798,10 @@
       <c r="D49" t="s">
         <v>270</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="18">
         <v>26</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="18" t="s">
         <v>109</v>
       </c>
       <c r="G49" t="s">
@@ -3545,15 +3816,15 @@
       <c r="J49" t="s">
         <v>95</v>
       </c>
-      <c r="K49" s="20">
+      <c r="K49" s="18">
         <v>58.4</v>
       </c>
       <c r="M49" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="24" t="s">
+    <row r="50" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="22" t="s">
         <v>256</v>
       </c>
       <c r="B50" t="s">
@@ -3565,10 +3836,10 @@
       <c r="D50" t="s">
         <v>271</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="18">
         <v>42</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="F50" s="18" t="s">
         <v>109</v>
       </c>
       <c r="G50" t="s">
@@ -3583,15 +3854,15 @@
       <c r="J50" t="s">
         <v>95</v>
       </c>
-      <c r="K50" s="20">
+      <c r="K50" s="18">
         <v>46</v>
       </c>
       <c r="M50" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="24" t="s">
+    <row r="51" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="22" t="s">
         <v>256</v>
       </c>
       <c r="B51" t="s">
@@ -3603,7 +3874,7 @@
       <c r="D51" t="s">
         <v>272</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="18">
         <v>24</v>
       </c>
       <c r="F51" t="s">
@@ -3621,15 +3892,15 @@
       <c r="J51" t="s">
         <v>95</v>
       </c>
-      <c r="K51" s="20">
+      <c r="K51" s="18">
         <v>28.1</v>
       </c>
       <c r="M51" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
+    <row r="52" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="22" t="s">
         <v>256</v>
       </c>
       <c r="B52" t="s">
@@ -3659,15 +3930,15 @@
       <c r="J52" t="s">
         <v>94</v>
       </c>
-      <c r="K52" s="31" t="s">
+      <c r="K52" s="19" t="s">
         <v>218</v>
       </c>
       <c r="M52" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="24" t="s">
+    <row r="53" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="22" t="s">
         <v>256</v>
       </c>
       <c r="B53" t="s">
@@ -3697,15 +3968,15 @@
       <c r="J53" t="s">
         <v>94</v>
       </c>
-      <c r="K53" s="31" t="s">
+      <c r="K53" s="19" t="s">
         <v>218</v>
       </c>
       <c r="M53" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="24" t="s">
+    <row r="54" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="22" t="s">
         <v>256</v>
       </c>
       <c r="B54" t="s">
@@ -3735,7 +4006,7 @@
       <c r="J54" t="s">
         <v>94</v>
       </c>
-      <c r="K54" s="31" t="s">
+      <c r="K54" s="19" t="s">
         <v>218</v>
       </c>
       <c r="M54" t="s">
@@ -3753,19 +4024,739 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE3B00C-19EB-F244-AB81-0213FAFEC4B4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52E614A-514A-114E-8972-B06F30BD00D9}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>32</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="4">
+        <v>33.6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="4">
+        <v>24.1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="4">
+        <v>24.4</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="4">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="4">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="4">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="4">
+        <v>44.6</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="4">
+        <v>44.7</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
+        <v>33</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>31</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="4">
+        <v>24.1</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="4">
+        <v>28.1</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>24</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="4">
+        <v>42.8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>42</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
+        <v>40</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
+        <v>42</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4">
+        <v>47</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5">
+        <v>49</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4">
+        <v>39</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4">
+        <v>42</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F736B67-149A-9645-81D7-20AD986C4783}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D023BC-CF53-EA43-BB00-ED33E3AC978C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B678B58-7994-8A40-A2D6-D3E124507B3C}">
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="48.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="48.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.77734375" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>126</v>
       </c>
@@ -3781,11 +4772,11 @@
       <c r="E1" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="16" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>131</v>
       </c>
@@ -3802,7 +4793,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>135</v>
       </c>
@@ -3819,7 +4810,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>138</v>
       </c>
@@ -3836,7 +4827,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>140</v>
       </c>
@@ -3853,7 +4844,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>142</v>
       </c>
@@ -3870,7 +4861,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>144</v>
       </c>
@@ -3887,7 +4878,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>146</v>
       </c>
@@ -3904,7 +4895,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>147</v>
       </c>
@@ -3921,7 +4912,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
@@ -3938,7 +4929,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>149</v>
       </c>
@@ -3955,7 +4946,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>150</v>
       </c>
@@ -3972,7 +4963,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>152</v>
       </c>
@@ -3989,7 +4980,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>153</v>
       </c>
@@ -4006,7 +4997,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>154</v>
       </c>
@@ -4023,7 +5014,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>156</v>
       </c>
@@ -4040,7 +5031,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>157</v>
       </c>
@@ -4057,7 +5048,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>158</v>
       </c>
@@ -4074,7 +5065,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>159</v>
       </c>
@@ -4091,7 +5082,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>160</v>
       </c>
@@ -4108,7 +5099,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>161</v>
       </c>
@@ -4125,7 +5116,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>163</v>
       </c>
@@ -4142,7 +5133,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>164</v>
       </c>
@@ -4159,7 +5150,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>165</v>
       </c>
@@ -4176,7 +5167,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>166</v>
       </c>
@@ -4193,7 +5184,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
         <v>169</v>
       </c>
@@ -4210,7 +5201,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>170</v>
       </c>
@@ -4227,7 +5218,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>171</v>
       </c>
@@ -4244,7 +5235,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
         <v>173</v>
       </c>
@@ -4261,7 +5252,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
         <v>174</v>
       </c>
@@ -4278,7 +5269,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
         <v>175</v>
       </c>
@@ -4295,7 +5286,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
         <v>177</v>
       </c>
@@ -4312,7 +5303,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="13" t="s">
         <v>178</v>
       </c>
@@ -4329,7 +5320,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="13" t="s">
         <v>179</v>
       </c>
@@ -4346,7 +5337,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="13" t="s">
         <v>180</v>
       </c>
@@ -4363,7 +5354,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="13" t="s">
         <v>181</v>
       </c>
@@ -4380,7 +5371,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="13" t="s">
         <v>182</v>
       </c>
@@ -4397,7 +5388,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>183</v>
       </c>
@@ -4414,7 +5405,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="13" t="s">
         <v>184</v>
       </c>
@@ -4431,7 +5422,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="13" t="s">
         <v>185</v>
       </c>
@@ -4448,7 +5439,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="13" t="s">
         <v>186</v>
       </c>
@@ -4465,7 +5456,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="13" t="s">
         <v>187</v>
       </c>
@@ -4482,7 +5473,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
         <v>188</v>
       </c>
@@ -4499,7 +5490,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="13" t="s">
         <v>189</v>
       </c>
@@ -4516,7 +5507,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>190</v>
       </c>
@@ -4533,7 +5524,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
         <v>191</v>
       </c>
@@ -4550,7 +5541,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
         <v>192</v>
       </c>
@@ -4567,7 +5558,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="13" t="s">
         <v>193</v>
       </c>
@@ -4584,7 +5575,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="13" t="s">
         <v>194</v>
       </c>
@@ -4601,7 +5592,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="13" t="s">
         <v>196</v>
       </c>
@@ -4618,7 +5609,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="13" t="s">
         <v>197</v>
       </c>
@@ -4635,7 +5626,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="13" t="s">
         <v>198</v>
       </c>
@@ -4657,792 +5648,791 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC0462BB-2EF8-744E-A457-D2CA86DE6E2E}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="21.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.21875" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.44140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="21.109375" style="17"/>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.83203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.5" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="16" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="18">
         <v>30</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="18">
         <v>28.4</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="18">
         <v>4</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="18">
         <v>6.19</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="18" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>22</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="18">
         <v>28.1</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="18">
         <v>3</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="18">
         <v>6.28</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>26</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="18">
         <v>58.4</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="18">
         <v>4</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="18">
         <v>10.050000000000001</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="20" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="18">
         <v>42</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="18">
         <v>46</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="18">
         <v>4</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="18">
         <v>12.79</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="20" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="18">
         <v>24</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="18">
         <v>28.1</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="18">
         <v>3</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="18">
         <v>11.53</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="20" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <v>56</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="18">
         <v>24.6</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="18">
         <v>3</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="18">
         <v>9.16</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="18" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <v>27</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="18">
         <v>3.9</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="18">
         <v>2</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="18">
         <v>6.72</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="18" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="18">
         <v>59</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G9" s="20" t="s">
+      <c r="D9" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="18">
         <v>50</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="20">
+      <c r="D10" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="18">
         <v>3</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="18">
         <v>6.43</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="18">
         <v>28</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="20">
+      <c r="D11" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11" s="18">
         <v>4</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="18">
         <v>11.51</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:12" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="18">
         <v>52</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="18">
         <v>27.4</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="18">
         <v>4</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="18">
         <v>5.21</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="18" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="18">
         <v>23</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="18">
         <v>6.8</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="18">
         <v>2</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="18">
         <v>10.11</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="18" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H14" s="20" t="s">
+      <c r="B14" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J14" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H15" s="20" t="s">
+      <c r="B15" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H15" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H16" s="20" t="s">
+      <c r="B16" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J16" s="20" t="s">
+      <c r="J16" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H17" s="20" t="s">
+      <c r="B17" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H17" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H18" s="20" t="s">
+      <c r="B18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J18" s="20" t="s">
+      <c r="J18" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H19" s="20" t="s">
+      <c r="B19" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H19" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J19" s="20" t="s">
+      <c r="J19" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H20" s="20" t="s">
+      <c r="B20" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H21" s="20" t="s">
+      <c r="B21" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H21" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H22" s="20" t="s">
+      <c r="B22" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H22" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J22" s="20" t="s">
+      <c r="J22" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="18">
         <v>46</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="18">
         <v>26.1</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="18">
         <v>4</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="18">
         <v>8.65</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="18" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="18">
         <v>51</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="18">
         <v>43.6</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="18">
         <v>4</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="18">
         <v>7.2</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="18" t="s">
         <v>145</v>
       </c>
     </row>
@@ -5450,697 +6440,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52E614A-514A-114E-8972-B06F30BD00D9}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="5.77734375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="10.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4">
-        <v>32</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="4">
-        <v>33.6</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4">
-        <v>30</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="4">
-        <v>24.1</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4">
-        <v>31</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" s="4">
-        <v>24.4</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
-        <v>19</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="4">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4">
-        <v>49</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="4">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5">
-        <v>40</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5">
-        <v>28</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="4">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5">
-        <v>19</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="4">
-        <v>44.6</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5">
-        <v>34</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="4">
-        <v>44.7</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4">
-        <v>33</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="4">
-        <v>5.5</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="4">
-        <v>24.1</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4">
-        <v>22</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="4">
-        <v>28.1</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4">
-        <v>24</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" s="4">
-        <v>42.8</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4">
-        <v>42</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5">
-        <v>40</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4">
-        <v>42</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4">
-        <v>47</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5">
-        <v>49</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4">
-        <v>39</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4">
-        <v>27</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4">
-        <v>42</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>